--- a/artfynd/A 31206-2023 artfynd.xlsx
+++ b/artfynd/A 31206-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31206-2023 artfynd.xlsx
+++ b/artfynd/A 31206-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96972081</v>
+        <v>96972132</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björnberget, Ång</t>
+          <t>Björnberget, Kälkåsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687637.7742836676</v>
+        <v>687804</v>
       </c>
       <c r="R2" t="n">
-        <v>7092388.131559911</v>
+        <v>7092268</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2021-10-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,37 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96972132</v>
+        <v>96972081</v>
       </c>
       <c r="B3" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,14 +814,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnberget, Kälkåsen, Ång</t>
+          <t>Björnberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>687804.5176888561</v>
+        <v>687638</v>
       </c>
       <c r="R3" t="n">
-        <v>7092267.539042591</v>
+        <v>7092388</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +851,9 @@
           <t>2021-10-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,6 +882,355 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>55683421</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>687954</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7092179</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96972211</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björnberget, Kälkåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>687956</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7092176</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-10-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>55683420</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>687954</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7092179</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2015-06-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
